--- a/Result/profitability/4747.xlsx
+++ b/Result/profitability/4747.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0.56875</v>
+        <v>0.5387500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>41.8575</v>
+        <v>41.39125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5625</v>
+        <v>0.53625</v>
       </c>
       <c r="N3" t="n">
-        <v>43.06625</v>
+        <v>42.5825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5287499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>44.0575</v>
+        <v>43.68125000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5874999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="N5" t="n">
-        <v>44.35625</v>
+        <v>44.02375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6125</v>
       </c>
       <c r="N6" t="n">
-        <v>45.60875</v>
+        <v>45.15625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.79</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6825</v>
+        <v>0.72</v>
       </c>
       <c r="N7" t="n">
-        <v>46.65125</v>
+        <v>46.36625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>99.40000000000001</v>
@@ -8810,6 +8810,133 @@
       </c>
       <c r="AM66" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4747</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>147</v>
+      </c>
+      <c r="D67" t="n">
+        <v>92</v>
+      </c>
+      <c r="E67" t="n">
+        <v>55</v>
+      </c>
+      <c r="F67" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>16</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>12</v>
+      </c>
+      <c r="K67" t="n">
+        <v>10</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="N67" t="n">
+        <v>39.92125</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-0.8424657534246576</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>-2.599999999999994</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.06532663316582898</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.4651162790697674</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-2.659999999999997</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-0.06673356748620163</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
